--- a/data/trans_orig/P39C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>51939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85180</t>
+          <t>84171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77739</t>
+          <t>78668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113385</t>
+          <t>113604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78263</t>
+          <t>79807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112130</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>167751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214218</t>
+          <t>214039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96230</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>133110</t>
+          <t>131097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75755</t>
+          <t>75528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>108516</t>
+          <t>109869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181265</t>
+          <t>182865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>230324</t>
+          <t>232168</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30686</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55679</t>
+          <t>55487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71269</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108307</t>
+          <t>108325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>47087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40321</t>
+          <t>39950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67384</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134172</t>
+          <t>133476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48559</t>
+          <t>48861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52048</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83464</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72694</t>
+          <t>73482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104404</t>
+          <t>106058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>91925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143612</t>
+          <t>144439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186695</t>
+          <t>193295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71070</t>
+          <t>71813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102910</t>
+          <t>103585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84611</t>
+          <t>83328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>118522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>164314</t>
+          <t>166442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>211157</t>
+          <t>212829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57729</t>
+          <t>56860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>49310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64052</t>
+          <t>65929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99784</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>45702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73727</t>
+          <t>73868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77967</t>
+          <t>77123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101495</t>
+          <t>102285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141801</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64132</t>
+          <t>65667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>91685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126810</t>
+          <t>129073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22929</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121722</t>
+          <t>121918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163368</t>
+          <t>161828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108818</t>
+          <t>107555</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147207</t>
+          <t>146971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>52518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145295</t>
+          <t>147406</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>190212</t>
+          <t>190291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57514</t>
+          <t>57836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>90419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>27768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73219</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108469</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63474</t>
+          <t>64695</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96806</t>
+          <t>97818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>53201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100825</t>
+          <t>101176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140048</t>
+          <t>139335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92900</t>
+          <t>93373</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131665</t>
+          <t>133864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55082</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86350</t>
+          <t>87794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155556</t>
+          <t>157887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207091</t>
+          <t>209215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222451</t>
+          <t>222833</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274630</t>
+          <t>279416</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170226</t>
+          <t>171136</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216323</t>
+          <t>218137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406659</t>
+          <t>405108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>478019</t>
+          <t>478261</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>229361</t>
+          <t>230691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>283274</t>
+          <t>285558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171796</t>
+          <t>170373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>220108</t>
+          <t>218291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>414340</t>
+          <t>414530</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>484047</t>
+          <t>490006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116228</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156685</t>
+          <t>156133</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66499</t>
+          <t>66717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98532</t>
+          <t>100962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194031</t>
+          <t>191194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>247643</t>
+          <t>246170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145062</t>
+          <t>142886</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191387</t>
+          <t>191485</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126035</t>
+          <t>124908</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>171536</t>
+          <t>168700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280970</t>
+          <t>282901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>345853</t>
+          <t>350491</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51058</t>
+          <t>50271</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80649</t>
+          <t>80465</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>47747</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77485</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>105872</t>
+          <t>103736</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>148868</t>
+          <t>146491</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101975</t>
+          <t>99947</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139906</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119285</t>
+          <t>121342</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>160196</t>
+          <t>162914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230748</t>
+          <t>234259</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>288731</t>
+          <t>291001</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130911</t>
+          <t>130114</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>171445</t>
+          <t>171729</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>180898</t>
+          <t>181918</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>227834</t>
+          <t>227184</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>324257</t>
+          <t>322731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>383328</t>
+          <t>387498</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75946</t>
+          <t>74366</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70436</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>105757</t>
+          <t>103125</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>124359</t>
+          <t>126603</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>169052</t>
+          <t>170784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>71631</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>105411</t>
+          <t>105181</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>117679</t>
+          <t>119119</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>161473</t>
+          <t>159597</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>198727</t>
+          <t>202140</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>252919</t>
+          <t>255501</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>32371</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>66945</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>58912</t>
+          <t>59128</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>94503</t>
+          <t>92863</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>48306</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>70589</t>
+          <t>71457</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>210912</t>
+          <t>209970</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>264431</t>
+          <t>263203</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>265581</t>
+          <t>265304</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>326753</t>
+          <t>325277</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>43875</t>
+          <t>44395</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>250788</t>
+          <t>252373</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>308242</t>
+          <t>308774</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>280122</t>
+          <t>282863</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>344960</t>
+          <t>344546</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>136384</t>
+          <t>136491</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>184689</t>
+          <t>186455</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>145657</t>
+          <t>147346</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>198352</t>
+          <t>196624</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>162639</t>
+          <t>163617</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>213255</t>
+          <t>216544</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>178880</t>
+          <t>183448</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>233863</t>
+          <t>232851</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>279586</t>
+          <t>279232</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>346091</t>
+          <t>348625</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>223800</t>
+          <t>222158</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>282292</t>
+          <t>283475</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>514997</t>
+          <t>521958</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>610771</t>
+          <t>611056</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>675395</t>
+          <t>679728</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>769357</t>
+          <t>771430</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>726736</t>
+          <t>725755</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>822711</t>
+          <t>823763</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1426637</t>
+          <t>1438499</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1564485</t>
+          <t>1562033</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>719987</t>
+          <t>722610</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>811421</t>
+          <t>813859</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>856408</t>
+          <t>860738</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>967858</t>
+          <t>963465</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1614940</t>
+          <t>1604663</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1755648</t>
+          <t>1742695</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>330648</t>
+          <t>329056</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>402552</t>
+          <t>400347</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>391715</t>
+          <t>389350</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>469702</t>
+          <t>470191</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>740207</t>
+          <t>738087</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>845656</t>
+          <t>851130</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>432516</t>
+          <t>432106</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>506498</t>
+          <t>511336</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>582422</t>
+          <t>582776</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>674600</t>
+          <t>674566</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1040254</t>
+          <t>1042161</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1162921</t>
+          <t>1160755</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17325</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61328</t>
+          <t>60618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>91108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128539</t>
+          <t>127193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,47 +5867,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>21,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>97910</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84182</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>113426</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>21,17%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97910</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82654</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>112756</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185098</t>
+          <t>184499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232998</t>
+          <t>231675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126549</t>
+          <t>125609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>166439</t>
+          <t>165204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98002</t>
+          <t>96636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127528</t>
+          <t>126307</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231181</t>
+          <t>232229</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>278723</t>
+          <t>281465</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81901</t>
+          <t>81266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61186</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87495</t>
+          <t>85471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119999</t>
+          <t>120437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156970</t>
+          <t>160471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67822</t>
+          <t>68549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99517</t>
+          <t>99625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81354</t>
+          <t>82809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111403</t>
+          <t>112868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158885</t>
+          <t>157687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201498</t>
+          <t>203041</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>32199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>62415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78047</t>
+          <t>77351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112651</t>
+          <t>111898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69131</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96062</t>
+          <t>95394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155522</t>
+          <t>156745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202151</t>
+          <t>200781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87106</t>
+          <t>86966</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123018</t>
+          <t>123285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94600</t>
+          <t>94656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123630</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>190833</t>
+          <t>191451</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236942</t>
+          <t>237639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57957</t>
+          <t>57908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89557</t>
+          <t>88067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46164</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>68777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>111724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148267</t>
+          <t>151802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72177</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104709</t>
+          <t>104431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>51610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76711</t>
+          <t>74767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170057</t>
+          <t>169993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>39394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,47 +7118,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12489</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18728</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>12489</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>8204</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>18920</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52504</t>
+          <t>52009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91810</t>
+          <t>92198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126726</t>
+          <t>127587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>43024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124605</t>
+          <t>124814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162394</t>
+          <t>165271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82934</t>
+          <t>84378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114620</t>
+          <t>116516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34282</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51213</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122333</t>
+          <t>123692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157798</t>
+          <t>160311</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53316</t>
+          <t>51754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79671</t>
+          <t>79400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,47 +7492,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>89997</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>75753</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>105842</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>20,52%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>89997</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>75248</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>106033</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>51133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77683</t>
+          <t>78953</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86392</t>
+          <t>85614</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119489</t>
+          <t>119884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>51491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85666</t>
+          <t>84825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>82271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>85492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153563</t>
+          <t>156752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179157</t>
+          <t>178725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233566</t>
+          <t>233179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83007</t>
+          <t>83902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223436</t>
+          <t>222728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>255630</t>
+          <t>232573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>433216</t>
+          <t>432241</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>219852</t>
+          <t>221274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274929</t>
+          <t>277825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>271875</t>
+          <t>274121</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>656578</t>
+          <t>651587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>510872</t>
+          <t>513044</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>991114</t>
+          <t>1021070</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129198</t>
+          <t>129920</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175300</t>
+          <t>172581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51249</t>
+          <t>48116</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132052</t>
+          <t>133405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>172135</t>
+          <t>167824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>295304</t>
+          <t>298147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>145954</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189548</t>
+          <t>189709</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67794</t>
+          <t>67906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>193123</t>
+          <t>190155</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>203999</t>
+          <t>210778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>361143</t>
+          <t>364321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56677</t>
+          <t>55418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59044</t>
+          <t>57608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71703</t>
+          <t>71704</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>108056</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76414</t>
+          <t>77866</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110105</t>
+          <t>111624</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>120308</t>
+          <t>119641</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163301</t>
+          <t>164583</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205819</t>
+          <t>204853</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>261199</t>
+          <t>263953</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94314</t>
+          <t>95551</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135240</t>
+          <t>134577</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>183906</t>
+          <t>183513</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>296521</t>
+          <t>295312</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>291733</t>
+          <t>290330</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>411191</t>
+          <t>396705</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>70545</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>90507</t>
+          <t>91282</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>126166</t>
+          <t>126248</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>140450</t>
+          <t>143713</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>185515</t>
+          <t>186088</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58137</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88269</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140787</t>
+          <t>141064</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>190370</t>
+          <t>189476</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>211859</t>
+          <t>214060</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>265920</t>
+          <t>264959</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>65177</t>
+          <t>62598</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>56595</t>
+          <t>57207</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>96494</t>
+          <t>98529</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>50833</t>
+          <t>51305</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>138364</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>180764</t>
+          <t>181797</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>167839</t>
+          <t>168731</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>219353</t>
+          <t>221789</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -9375,12 +9375,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>46857</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>148902</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>187215</t>
+          <t>188208</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>175582</t>
+          <t>175966</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>223178</t>
+          <t>225334</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -9488,12 +9488,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>88769</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>118707</t>
+          <t>119486</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>93829</t>
+          <t>91891</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>127357</t>
+          <t>128599</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>115248</t>
+          <t>114893</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>149883</t>
+          <t>149362</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>120189</t>
+          <t>120082</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>157942</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -9831,12 +9831,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>184666</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>248401</t>
+          <t>246780</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>166420</t>
+          <t>167067</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>239414</t>
+          <t>240276</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>367493</t>
+          <t>370166</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>469410</t>
+          <t>468014</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>594036</t>
+          <t>601539</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>694015</t>
+          <t>688773</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>540389</t>
+          <t>536823</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>751574</t>
+          <t>750788</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1166774</t>
+          <t>1144140</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1403614</t>
+          <t>1403667</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>691583</t>
+          <t>688634</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>789008</t>
+          <t>785929</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10072,12 +10072,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>902232</t>
+          <t>895077</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1534728</t>
+          <t>1503749</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1627681</t>
+          <t>1639109</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2295221</t>
+          <t>2287067</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>380422</t>
+          <t>383068</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>455982</t>
+          <t>457734</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>354306</t>
+          <t>374048</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>510663</t>
+          <t>515664</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>771660</t>
+          <t>781530</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>944763</t>
+          <t>941809</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>434018</t>
+          <t>437103</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>511112</t>
+          <t>512704</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>497350</t>
+          <t>496475</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>700355</t>
+          <t>702728</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>981396</t>
+          <t>987720</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1190089</t>
+          <t>1185140</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>29556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51939</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84171</t>
+          <t>84244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78668</t>
+          <t>78772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113604</t>
+          <t>114441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79807</t>
+          <t>79157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111627</t>
+          <t>111821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167751</t>
+          <t>167889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214039</t>
+          <t>216569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94738</t>
+          <t>94432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131097</t>
+          <t>131357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75528</t>
+          <t>75598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109869</t>
+          <t>108232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>182865</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232168</t>
+          <t>228223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>56490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>61239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>71982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108325</t>
+          <t>109040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47087</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76821</t>
+          <t>76463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39950</t>
+          <t>40669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67334</t>
+          <t>66979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95388</t>
+          <t>94431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133476</t>
+          <t>134268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42530</t>
+          <t>41191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50809</t>
+          <t>51652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84669</t>
+          <t>83445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106058</t>
+          <t>106419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>63179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91925</t>
+          <t>94049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144439</t>
+          <t>144224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193295</t>
+          <t>187763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71813</t>
+          <t>73302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103585</t>
+          <t>105545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83328</t>
+          <t>85664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118522</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>166442</t>
+          <t>166604</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>212829</t>
+          <t>212597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56860</t>
+          <t>56245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65929</t>
+          <t>64547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73868</t>
+          <t>74557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77123</t>
+          <t>76460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102285</t>
+          <t>99615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>139833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54713</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38326</t>
+          <t>36320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65667</t>
+          <t>63017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91685</t>
+          <t>89938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129073</t>
+          <t>126151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44151</t>
+          <t>43347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121918</t>
+          <t>122387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161828</t>
+          <t>163370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107555</t>
+          <t>107782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146971</t>
+          <t>145500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>30818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147406</t>
+          <t>148090</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>190291</t>
+          <t>190953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57836</t>
+          <t>57019</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90419</t>
+          <t>89963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71687</t>
+          <t>71137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108915</t>
+          <t>107805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>63763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97818</t>
+          <t>96468</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53201</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101176</t>
+          <t>100885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139335</t>
+          <t>139926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>93180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133864</t>
+          <t>133574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157887</t>
+          <t>157764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209215</t>
+          <t>206571</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222833</t>
+          <t>223739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279416</t>
+          <t>276823</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171136</t>
+          <t>170411</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>218137</t>
+          <t>218280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>405108</t>
+          <t>409843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>478261</t>
+          <t>480404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230691</t>
+          <t>231159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285558</t>
+          <t>282505</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170373</t>
+          <t>171887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>218291</t>
+          <t>218357</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>414530</t>
+          <t>417669</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>490006</t>
+          <t>494503</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113536</t>
+          <t>116592</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156133</t>
+          <t>159948</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66717</t>
+          <t>64926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100962</t>
+          <t>99111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>191194</t>
+          <t>192973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>247114</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142886</t>
+          <t>144946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191485</t>
+          <t>192903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>124908</t>
+          <t>126656</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>168700</t>
+          <t>168030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282901</t>
+          <t>281551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>350491</t>
+          <t>347942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50271</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>80960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47747</t>
+          <t>46761</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76927</t>
+          <t>79040</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>103736</t>
+          <t>105067</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>146491</t>
+          <t>147327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99947</t>
+          <t>101954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137725</t>
+          <t>140297</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>121342</t>
+          <t>118143</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>162914</t>
+          <t>162711</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234259</t>
+          <t>230428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>291001</t>
+          <t>290161</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130114</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>171729</t>
+          <t>170407</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>181918</t>
+          <t>180637</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>227184</t>
+          <t>228628</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>322731</t>
+          <t>324366</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>387498</t>
+          <t>388576</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>74366</t>
+          <t>75731</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70251</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>103125</t>
+          <t>104312</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>126603</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>170784</t>
+          <t>169767</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>71631</t>
+          <t>72696</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>105181</t>
+          <t>106276</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>119119</t>
+          <t>115372</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>159597</t>
+          <t>159076</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>202140</t>
+          <t>201284</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>255501</t>
+          <t>255525</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>66945</t>
+          <t>67186</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>59128</t>
+          <t>59822</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>92863</t>
+          <t>95416</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>48653</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>71457</t>
+          <t>71996</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>209970</t>
+          <t>211098</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>263203</t>
+          <t>263723</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>265304</t>
+          <t>266668</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>325277</t>
+          <t>327377</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>24044</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44395</t>
+          <t>44175</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>252373</t>
+          <t>248396</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>308774</t>
+          <t>306663</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>282863</t>
+          <t>283543</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>344546</t>
+          <t>346386</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>136491</t>
+          <t>134794</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>186455</t>
+          <t>185114</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>147346</t>
+          <t>147732</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>196624</t>
+          <t>196849</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>26589</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>163617</t>
+          <t>164881</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>216544</t>
+          <t>218213</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>183448</t>
+          <t>179537</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>232851</t>
+          <t>233867</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>279232</t>
+          <t>278831</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>347051</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>222158</t>
+          <t>220534</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>283475</t>
+          <t>284749</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>521958</t>
+          <t>516083</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>611056</t>
+          <t>608829</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>679728</t>
+          <t>676601</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>771430</t>
+          <t>768103</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>725755</t>
+          <t>727486</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>823763</t>
+          <t>824750</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1438499</t>
+          <t>1426165</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1562033</t>
+          <t>1564451</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>722610</t>
+          <t>720570</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>813859</t>
+          <t>813703</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>860738</t>
+          <t>857597</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>963465</t>
+          <t>961267</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1604663</t>
+          <t>1609932</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1742695</t>
+          <t>1751352</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>329056</t>
+          <t>328700</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>400347</t>
+          <t>402320</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>389350</t>
+          <t>389043</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>470191</t>
+          <t>466488</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>738087</t>
+          <t>745097</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>851130</t>
+          <t>846354</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>432106</t>
+          <t>433303</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>511336</t>
+          <t>511091</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,47 +5290,47 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>630008</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>580915</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>677070</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
           <t>19,4%</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>630008</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>582776</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>674566</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1042161</t>
+          <t>1037653</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1160755</t>
+          <t>1164257</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -5734,32 +5734,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>30796</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5769,32 +5769,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19550</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5804,32 +5804,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46236</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34959</t>
+          <t>37584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60618</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -5847,32 +5847,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>109029</t>
+          <t>115294</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91108</t>
+          <t>97357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5882,32 +5882,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97910</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84182</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113426</t>
+          <t>119951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5917,32 +5917,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>206939</t>
+          <t>219498</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184499</t>
+          <t>195405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231675</t>
+          <t>246399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -5960,32 +5960,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>158648</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>139573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165204</t>
+          <t>181296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5995,32 +5995,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111035</t>
+          <t>120236</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96636</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>135572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6030,32 +6030,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256290</t>
+          <t>278884</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232229</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281465</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -6073,32 +6073,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66228</t>
+          <t>73861</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52328</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81266</t>
+          <t>91005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6108,32 +6108,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>83407</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60321</t>
+          <t>69778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>97371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>139081</t>
+          <t>157268</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120437</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160471</t>
+          <t>177753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -6186,32 +6186,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82529</t>
+          <t>89757</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68549</t>
+          <t>75248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99625</t>
+          <t>109854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6221,22 +6221,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>96370</t>
+          <t>104560</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82809</t>
+          <t>90181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112868</t>
+          <t>121515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6256,32 +6256,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>178899</t>
+          <t>194317</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157687</t>
+          <t>171641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203041</t>
+          <t>217121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -6299,17 +6299,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>429726</t>
+          <t>468357</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>429726</t>
+          <t>468357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>429726</t>
+          <t>468357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6334,17 +6334,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>397718</t>
+          <t>433094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>397718</t>
+          <t>433094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>397718</t>
+          <t>433094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>827444</t>
+          <t>901451</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>827444</t>
+          <t>901451</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>827444</t>
+          <t>901451</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,32 +6416,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6451,32 +6451,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6486,32 +6486,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48016</t>
+          <t>53737</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>40992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62415</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -6529,32 +6529,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94938</t>
+          <t>103934</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77351</t>
+          <t>87343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111898</t>
+          <t>123433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6564,32 +6564,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82192</t>
+          <t>92334</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95394</t>
+          <t>107280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6599,32 +6599,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>177130</t>
+          <t>196268</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156745</t>
+          <t>173043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200781</t>
+          <t>221545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -6642,32 +6642,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103585</t>
+          <t>108456</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86966</t>
+          <t>90699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123285</t>
+          <t>127374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6677,32 +6677,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>108933</t>
+          <t>117465</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>102668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>133123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6712,32 +6712,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>212517</t>
+          <t>225920</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>191451</t>
+          <t>202473</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237639</t>
+          <t>250024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6755,32 +6755,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72628</t>
+          <t>77636</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57908</t>
+          <t>61405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88067</t>
+          <t>95015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6790,32 +6790,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56637</t>
+          <t>62611</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>51500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68777</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>129265</t>
+          <t>140247</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111724</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151802</t>
+          <t>161914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -6868,32 +6868,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>86554</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>72375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104431</t>
+          <t>104087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6903,32 +6903,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63056</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51610</t>
+          <t>58340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>83541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6938,32 +6938,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>149610</t>
+          <t>158729</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130908</t>
+          <t>138965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169993</t>
+          <t>179407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -6981,17 +6981,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>383065</t>
+          <t>407081</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>383065</t>
+          <t>407081</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>383065</t>
+          <t>407081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>333473</t>
+          <t>367820</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>333473</t>
+          <t>367820</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>333473</t>
+          <t>367820</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>716538</t>
+          <t>774901</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>716538</t>
+          <t>774901</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>716538</t>
+          <t>774901</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>28382</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39394</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7133,32 +7133,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7168,32 +7168,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>42008</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52009</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -7211,32 +7211,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>109592</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92198</t>
+          <t>106431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127587</t>
+          <t>144369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7246,32 +7246,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43024</t>
+          <t>47492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7281,32 +7281,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>143824</t>
+          <t>163606</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124814</t>
+          <t>144305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165271</t>
+          <t>187398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -7324,32 +7324,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98716</t>
+          <t>106179</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84378</t>
+          <t>88020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116516</t>
+          <t>121615</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7359,32 +7359,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50680</t>
+          <t>55958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7394,32 +7394,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>140375</t>
+          <t>152181</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123692</t>
+          <t>133031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>160311</t>
+          <t>172810</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -7437,32 +7437,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65500</t>
+          <t>73262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51754</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>88687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7472,32 +7472,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>33369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>89997</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75753</t>
+          <t>85244</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105842</t>
+          <t>118045</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -7550,32 +7550,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>63050</t>
+          <t>66018</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51133</t>
+          <t>52588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78953</t>
+          <t>81820</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7585,32 +7585,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>35766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>55240</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7620,32 +7620,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>101428</t>
+          <t>110854</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85614</t>
+          <t>94463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119884</t>
+          <t>129894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -7663,17 +7663,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>364441</t>
+          <t>398901</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>364441</t>
+          <t>398901</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>364441</t>
+          <t>398901</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>151256</t>
+          <t>169099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151256</t>
+          <t>169099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>151256</t>
+          <t>169099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7733,17 +7733,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>515696</t>
+          <t>567999</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>515696</t>
+          <t>567999</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>515696</t>
+          <t>567999</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7780,32 +7780,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>66702</t>
+          <t>78696</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51491</t>
+          <t>62277</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84825</t>
+          <t>98969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7815,32 +7815,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>62456</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82271</t>
+          <t>76470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7850,32 +7850,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>126172</t>
+          <t>141152</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>118822</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156752</t>
+          <t>163746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7893,32 +7893,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>203215</t>
+          <t>219322</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178725</t>
+          <t>190504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233179</t>
+          <t>245187</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7928,32 +7928,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>166551</t>
+          <t>183630</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83902</t>
+          <t>163327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>222728</t>
+          <t>204373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7963,32 +7963,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>369766</t>
+          <t>402951</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232573</t>
+          <t>368376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>432241</t>
+          <t>438651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -8006,32 +8006,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>247462</t>
+          <t>273427</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221274</t>
+          <t>246358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277825</t>
+          <t>305294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8041,32 +8041,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>420444</t>
+          <t>242992</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>274121</t>
+          <t>222664</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>651587</t>
+          <t>264923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8076,32 +8076,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>667906</t>
+          <t>516419</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>513044</t>
+          <t>481712</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1021070</t>
+          <t>552390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -8119,32 +8119,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>151585</t>
+          <t>159197</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129920</t>
+          <t>137062</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>172581</t>
+          <t>184134</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8154,32 +8154,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>97897</t>
+          <t>109795</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133405</t>
+          <t>127273</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>249482</t>
+          <t>268993</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167824</t>
+          <t>243341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>298147</t>
+          <t>299457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8232,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>167169</t>
+          <t>181450</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145954</t>
+          <t>157308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189709</t>
+          <t>206028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8267,32 +8267,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>142072</t>
+          <t>158451</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67906</t>
+          <t>140576</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190155</t>
+          <t>177310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8302,32 +8302,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>309241</t>
+          <t>339901</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>210778</t>
+          <t>309998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>364321</t>
+          <t>371175</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -8345,17 +8345,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>836134</t>
+          <t>912091</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>836134</t>
+          <t>912091</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>836134</t>
+          <t>912091</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8380,17 +8380,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>886434</t>
+          <t>757324</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>886434</t>
+          <t>757324</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>886434</t>
+          <t>757324</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8415,17 +8415,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1722568</t>
+          <t>1669415</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1722568</t>
+          <t>1669415</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1722568</t>
+          <t>1669415</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8462,32 +8462,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29597</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55418</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8497,32 +8497,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>45950</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>65189</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8532,32 +8532,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>87762</t>
+          <t>102009</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71704</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107381</t>
+          <t>123006</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -8575,32 +8575,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>93259</t>
+          <t>115601</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77866</t>
+          <t>96317</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111624</t>
+          <t>136180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8610,32 +8610,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>165390</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119641</t>
+          <t>148085</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>164583</t>
+          <t>187464</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8645,32 +8645,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>236703</t>
+          <t>280991</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204853</t>
+          <t>251325</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>263953</t>
+          <t>309293</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -8688,32 +8688,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>112519</t>
+          <t>116367</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95551</t>
+          <t>98584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134577</t>
+          <t>136420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8723,32 +8723,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>214189</t>
+          <t>205793</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>183513</t>
+          <t>185707</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>295312</t>
+          <t>226059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8758,32 +8758,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>326708</t>
+          <t>322160</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>290330</t>
+          <t>296914</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>396705</t>
+          <t>349890</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -8801,32 +8801,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>55070</t>
+          <t>62982</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42882</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>70545</t>
+          <t>79230</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8836,32 +8836,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>110002</t>
+          <t>121088</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>91282</t>
+          <t>105052</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>126248</t>
+          <t>137125</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8871,32 +8871,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>165072</t>
+          <t>184070</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>143713</t>
+          <t>163818</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>186088</t>
+          <t>208192</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8914,32 +8914,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>71161</t>
+          <t>80451</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58056</t>
+          <t>65496</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87785</t>
+          <t>98366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8949,32 +8949,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>169912</t>
+          <t>186216</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>167690</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>189476</t>
+          <t>207251</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8984,32 +8984,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>241073</t>
+          <t>266667</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>214060</t>
+          <t>239099</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>264959</t>
+          <t>291483</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -9027,17 +9027,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>373820</t>
+          <t>425596</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>373820</t>
+          <t>425596</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>373820</t>
+          <t>425596</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9062,17 +9062,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>683497</t>
+          <t>730302</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>683497</t>
+          <t>730302</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>683497</t>
+          <t>730302</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9097,17 +9097,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1057317</t>
+          <t>1155898</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1057317</t>
+          <t>1155898</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1057317</t>
+          <t>1155898</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9144,32 +9144,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9179,32 +9179,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>49708</t>
+          <t>52243</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62598</t>
+          <t>66018</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9214,32 +9214,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>74575</t>
+          <t>75576</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>57207</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>98529</t>
+          <t>95577</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -9257,32 +9257,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>51305</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9292,27 +9292,27 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>159977</t>
+          <t>174477</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>140736</t>
+          <t>155116</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>181797</t>
+          <t>196750</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -9327,32 +9327,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>192932</t>
+          <t>201661</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>168731</t>
+          <t>178324</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>221789</t>
+          <t>224112</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -9370,32 +9370,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9405,32 +9405,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>167692</t>
+          <t>180697</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>150204</t>
+          <t>161643</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>188208</t>
+          <t>202012</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9440,32 +9440,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>198290</t>
+          <t>206666</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>175966</t>
+          <t>182379</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>225334</t>
+          <t>233732</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -9483,32 +9483,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9518,32 +9518,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>103236</t>
+          <t>112996</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>97705</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>119486</t>
+          <t>132038</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>109504</t>
+          <t>118574</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>91891</t>
+          <t>101549</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>138069</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -9596,32 +9596,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9631,32 +9631,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>132561</t>
+          <t>143102</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>114893</t>
+          <t>125691</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>149362</t>
+          <t>161747</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>137688</t>
+          <t>147667</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>120082</t>
+          <t>128470</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>159785</t>
+          <t>166901</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -9709,17 +9709,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>99815</t>
+          <t>86630</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>99815</t>
+          <t>86630</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>99815</t>
+          <t>86630</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9744,17 +9744,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>613174</t>
+          <t>663515</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>613174</t>
+          <t>663515</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>613174</t>
+          <t>663515</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9779,17 +9779,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>712989</t>
+          <t>750145</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>712989</t>
+          <t>750145</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>712989</t>
+          <t>750145</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9826,32 +9826,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>213009</t>
+          <t>240020</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>182499</t>
+          <t>207242</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>246780</t>
+          <t>274983</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9861,32 +9861,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>209822</t>
+          <t>225947</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>167067</t>
+          <t>198873</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>240276</t>
+          <t>252775</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>422831</t>
+          <t>465966</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>370166</t>
+          <t>422605</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>468014</t>
+          <t>508794</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -9939,32 +9939,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>642987</t>
+          <t>706393</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>601539</t>
+          <t>659126</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>688773</t>
+          <t>753884</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9974,32 +9974,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>684307</t>
+          <t>758581</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>536823</t>
+          <t>720570</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>750788</t>
+          <t>804146</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10009,32 +10009,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1327294</t>
+          <t>1464975</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1144140</t>
+          <t>1401164</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1403667</t>
+          <t>1532466</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -10052,32 +10052,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>738135</t>
+          <t>789046</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>688634</t>
+          <t>740930</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>785929</t>
+          <t>844204</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10087,32 +10087,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1063951</t>
+          <t>913184</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>895077</t>
+          <t>871295</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1503749</t>
+          <t>957636</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1802086</t>
+          <t>1702230</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1639109</t>
+          <t>1643956</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2287067</t>
+          <t>1777816</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -10165,32 +10165,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>417279</t>
+          <t>452518</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>383068</t>
+          <t>409943</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>457734</t>
+          <t>490299</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10200,32 +10200,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>465122</t>
+          <t>515986</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>374048</t>
+          <t>482500</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>515664</t>
+          <t>552386</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>882401</t>
+          <t>968504</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>781530</t>
+          <t>921310</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>941809</t>
+          <t>1027067</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -10278,32 +10278,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>475590</t>
+          <t>510678</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>437103</t>
+          <t>473215</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>512704</t>
+          <t>553388</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10313,32 +10313,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>642349</t>
+          <t>707456</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>496475</t>
+          <t>665557</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>702728</t>
+          <t>746224</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1117939</t>
+          <t>1218135</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>987720</t>
+          <t>1159565</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1185140</t>
+          <t>1276757</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -10391,17 +10391,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2487001</t>
+          <t>2698655</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2487001</t>
+          <t>2698655</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2487001</t>
+          <t>2698655</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10426,17 +10426,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3065551</t>
+          <t>3121154</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3065551</t>
+          <t>3121154</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3065551</t>
+          <t>3121154</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10461,17 +10461,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>5552552</t>
+          <t>5819809</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>5552552</t>
+          <t>5819809</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5552552</t>
+          <t>5819809</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
